--- a/artfynd/A 8515-2023 artfynd.xlsx
+++ b/artfynd/A 8515-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8515-2023 artfynd.xlsx
+++ b/artfynd/A 8515-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1663,10 +1663,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107234819</v>
+        <v>107235175</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
+        <v>78596</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1675,41 +1675,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bergtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411404.3107922736</v>
+        <v>411460.8127294475</v>
       </c>
       <c r="R10" t="n">
-        <v>7012136.002775409</v>
+        <v>7012005.891864836</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1741,7 +1739,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1751,7 +1749,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1760,24 +1758,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1791,119 +1773,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>107235175</v>
-      </c>
-      <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bergtjärnen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>411460.8127294475</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7012005.891864836</v>
-      </c>
-      <c r="S11" t="n">
-        <v>25</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Undersåker</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-03-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Matilda Pettersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
